--- a/v.6.4.1/test_data/total_latest.xlsx
+++ b/v.6.4.1/test_data/total_latest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1008"/>
+  <dimension ref="A1:J1015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32009,7 +32009,7 @@
         <v>46279</v>
       </c>
       <c r="B987" t="n">
-        <v>32921</v>
+        <v>32919</v>
       </c>
       <c r="C987" t="n">
         <v>6217</v>
@@ -32027,7 +32027,7 @@
         <v>15042</v>
       </c>
       <c r="H987" t="n">
-        <v>5268</v>
+        <v>5266</v>
       </c>
       <c r="I987" t="n">
         <v>10708</v>
@@ -32041,7 +32041,7 @@
         <v>46280</v>
       </c>
       <c r="B988" t="n">
-        <v>31245</v>
+        <v>31243</v>
       </c>
       <c r="C988" t="n">
         <v>5911</v>
@@ -32059,7 +32059,7 @@
         <v>13882</v>
       </c>
       <c r="H988" t="n">
-        <v>4571</v>
+        <v>4569</v>
       </c>
       <c r="I988" t="n">
         <v>11357</v>
@@ -32073,7 +32073,7 @@
         <v>46281</v>
       </c>
       <c r="B989" t="n">
-        <v>32239</v>
+        <v>32237</v>
       </c>
       <c r="C989" t="n">
         <v>6539</v>
@@ -32091,7 +32091,7 @@
         <v>14613</v>
       </c>
       <c r="H989" t="n">
-        <v>3807</v>
+        <v>3805</v>
       </c>
       <c r="I989" t="n">
         <v>12547</v>
@@ -32105,7 +32105,7 @@
         <v>46282</v>
       </c>
       <c r="B990" t="n">
-        <v>32321</v>
+        <v>32319</v>
       </c>
       <c r="C990" t="n">
         <v>7941</v>
@@ -32123,7 +32123,7 @@
         <v>13007</v>
       </c>
       <c r="H990" t="n">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="I990" t="n">
         <v>14746</v>
@@ -32137,7 +32137,7 @@
         <v>46283</v>
       </c>
       <c r="B991" t="n">
-        <v>30284</v>
+        <v>30282</v>
       </c>
       <c r="C991" t="n">
         <v>7851</v>
@@ -32155,7 +32155,7 @@
         <v>12172</v>
       </c>
       <c r="H991" t="n">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="I991" t="n">
         <v>14433</v>
@@ -32169,7 +32169,7 @@
         <v>46284</v>
       </c>
       <c r="B992" t="n">
-        <v>17663</v>
+        <v>17661</v>
       </c>
       <c r="C992" t="n">
         <v>3699</v>
@@ -32187,13 +32187,13 @@
         <v>8255</v>
       </c>
       <c r="H992" t="n">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="I992" t="n">
         <v>8111</v>
       </c>
       <c r="J992" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="993">
@@ -32201,7 +32201,7 @@
         <v>46285</v>
       </c>
       <c r="B993" t="n">
-        <v>25237</v>
+        <v>25235</v>
       </c>
       <c r="C993" t="n">
         <v>5658</v>
@@ -32219,13 +32219,13 @@
         <v>12646</v>
       </c>
       <c r="H993" t="n">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="I993" t="n">
         <v>9368</v>
       </c>
       <c r="J993" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="994">
@@ -32233,7 +32233,7 @@
         <v>46286</v>
       </c>
       <c r="B994" t="n">
-        <v>33074</v>
+        <v>33072</v>
       </c>
       <c r="C994" t="n">
         <v>7254</v>
@@ -32251,7 +32251,7 @@
         <v>15391</v>
       </c>
       <c r="H994" t="n">
-        <v>3800</v>
+        <v>3798</v>
       </c>
       <c r="I994" t="n">
         <v>12397</v>
@@ -32265,7 +32265,7 @@
         <v>46287</v>
       </c>
       <c r="B995" t="n">
-        <v>31269</v>
+        <v>31267</v>
       </c>
       <c r="C995" t="n">
         <v>7455</v>
@@ -32283,7 +32283,7 @@
         <v>12126</v>
       </c>
       <c r="H995" t="n">
-        <v>3660</v>
+        <v>3658</v>
       </c>
       <c r="I995" t="n">
         <v>14113</v>
@@ -32297,7 +32297,7 @@
         <v>46288</v>
       </c>
       <c r="B996" t="n">
-        <v>28359</v>
+        <v>28357</v>
       </c>
       <c r="C996" t="n">
         <v>8711</v>
@@ -32315,7 +32315,7 @@
         <v>8367</v>
       </c>
       <c r="H996" t="n">
-        <v>3295</v>
+        <v>3293</v>
       </c>
       <c r="I996" t="n">
         <v>15282</v>
@@ -32329,7 +32329,7 @@
         <v>46289</v>
       </c>
       <c r="B997" t="n">
-        <v>9284</v>
+        <v>9282</v>
       </c>
       <c r="C997" t="n">
         <v>16</v>
@@ -32347,13 +32347,13 @@
         <v>6054</v>
       </c>
       <c r="H997" t="n">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="I997" t="n">
         <v>27</v>
       </c>
       <c r="J997" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="998">
@@ -32361,7 +32361,7 @@
         <v>46291</v>
       </c>
       <c r="B998" t="n">
-        <v>9122</v>
+        <v>9120</v>
       </c>
       <c r="C998" t="n">
         <v>13</v>
@@ -32379,13 +32379,13 @@
         <v>6658</v>
       </c>
       <c r="H998" t="n">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="I998" t="n">
         <v>17</v>
       </c>
       <c r="J998" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="999">
@@ -32393,7 +32393,7 @@
         <v>46292</v>
       </c>
       <c r="B999" t="n">
-        <v>19933</v>
+        <v>19931</v>
       </c>
       <c r="C999" t="n">
         <v>5838</v>
@@ -32411,13 +32411,13 @@
         <v>8345</v>
       </c>
       <c r="H999" t="n">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="I999" t="n">
         <v>8902</v>
       </c>
       <c r="J999" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1000">
@@ -32425,7 +32425,7 @@
         <v>46293</v>
       </c>
       <c r="B1000" t="n">
-        <v>31780</v>
+        <v>31778</v>
       </c>
       <c r="C1000" t="n">
         <v>7700</v>
@@ -32443,7 +32443,7 @@
         <v>13544</v>
       </c>
       <c r="H1000" t="n">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="I1000" t="n">
         <v>12599</v>
@@ -32457,7 +32457,7 @@
         <v>46294</v>
       </c>
       <c r="B1001" t="n">
-        <v>33845</v>
+        <v>33843</v>
       </c>
       <c r="C1001" t="n">
         <v>6910</v>
@@ -32475,7 +32475,7 @@
         <v>11674</v>
       </c>
       <c r="H1001" t="n">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="I1001" t="n">
         <v>17865</v>
@@ -32489,7 +32489,7 @@
         <v>46295</v>
       </c>
       <c r="B1002" t="n">
-        <v>29391</v>
+        <v>29389</v>
       </c>
       <c r="C1002" t="n">
         <v>4962</v>
@@ -32507,7 +32507,7 @@
         <v>10766</v>
       </c>
       <c r="H1002" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="I1002" t="n">
         <v>14097</v>
@@ -32521,7 +32521,7 @@
         <v>46296</v>
       </c>
       <c r="B1003" t="n">
-        <v>39774</v>
+        <v>39772</v>
       </c>
       <c r="C1003" t="n">
         <v>7154</v>
@@ -32539,7 +32539,7 @@
         <v>14987</v>
       </c>
       <c r="H1003" t="n">
-        <v>4061</v>
+        <v>4059</v>
       </c>
       <c r="I1003" t="n">
         <v>19426</v>
@@ -32553,7 +32553,7 @@
         <v>46297</v>
       </c>
       <c r="B1004" t="n">
-        <v>36067</v>
+        <v>36064</v>
       </c>
       <c r="C1004" t="n">
         <v>7778</v>
@@ -32571,7 +32571,7 @@
         <v>11329</v>
       </c>
       <c r="H1004" t="n">
-        <v>4749</v>
+        <v>4746</v>
       </c>
       <c r="I1004" t="n">
         <v>18943</v>
@@ -32585,7 +32585,7 @@
         <v>46298</v>
       </c>
       <c r="B1005" t="n">
-        <v>25225</v>
+        <v>25223</v>
       </c>
       <c r="C1005" t="n">
         <v>6502</v>
@@ -32603,13 +32603,13 @@
         <v>10423</v>
       </c>
       <c r="H1005" t="n">
-        <v>2919</v>
+        <v>2917</v>
       </c>
       <c r="I1005" t="n">
         <v>11751</v>
       </c>
       <c r="J1005" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1006">
@@ -32617,7 +32617,7 @@
         <v>46299</v>
       </c>
       <c r="B1006" t="n">
-        <v>30240</v>
+        <v>30238</v>
       </c>
       <c r="C1006" t="n">
         <v>5751</v>
@@ -32635,13 +32635,13 @@
         <v>11779</v>
       </c>
       <c r="H1006" t="n">
-        <v>3578</v>
+        <v>3576</v>
       </c>
       <c r="I1006" t="n">
         <v>14730</v>
       </c>
       <c r="J1006" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1007">
@@ -32649,7 +32649,7 @@
         <v>46300</v>
       </c>
       <c r="B1007" t="n">
-        <v>28097</v>
+        <v>28095</v>
       </c>
       <c r="C1007" t="n">
         <v>6344</v>
@@ -32667,7 +32667,7 @@
         <v>11137</v>
       </c>
       <c r="H1007" t="n">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="I1007" t="n">
         <v>14307</v>
@@ -32681,13 +32681,13 @@
         <v>46301</v>
       </c>
       <c r="B1008" t="n">
-        <v>35492</v>
+        <v>35486</v>
       </c>
       <c r="C1008" t="n">
         <v>7556</v>
       </c>
       <c r="D1008" t="n">
-        <v>9509</v>
+        <v>9508</v>
       </c>
       <c r="E1008" t="n">
         <v>1606</v>
@@ -32699,13 +32699,237 @@
         <v>11806</v>
       </c>
       <c r="H1008" t="n">
-        <v>4404</v>
+        <v>4399</v>
       </c>
       <c r="I1008" t="n">
-        <v>17065</v>
+        <v>17064</v>
       </c>
       <c r="J1008" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1009" t="n">
+        <v>32729</v>
+      </c>
+      <c r="C1009" t="n">
+        <v>7744</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>9284</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>892</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>329</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>11574</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>2906</v>
+      </c>
+      <c r="I1009" t="n">
+        <v>17028</v>
+      </c>
+      <c r="J1009" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1010" t="n">
+        <v>30867</v>
+      </c>
+      <c r="C1010" t="n">
+        <v>7007</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>9189</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>839</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>273</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>10909</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>2650</v>
+      </c>
+      <c r="I1010" t="n">
+        <v>16196</v>
+      </c>
+      <c r="J1010" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1011" t="n">
+        <v>27438</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>6268</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>7915</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>166</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>10851</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>2238</v>
+      </c>
+      <c r="I1011" t="n">
+        <v>14183</v>
+      </c>
+      <c r="J1011" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1012" t="n">
+        <v>23970</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>5483</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>6967</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>469</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>8854</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>1847</v>
+      </c>
+      <c r="I1012" t="n">
+        <v>12450</v>
+      </c>
+      <c r="J1012" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1013" t="n">
+        <v>26891</v>
+      </c>
+      <c r="C1013" t="n">
+        <v>5106</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>6046</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>170</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>11495</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>4073</v>
+      </c>
+      <c r="I1013" t="n">
+        <v>11152</v>
+      </c>
+      <c r="J1013" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1014" t="n">
+        <v>35396</v>
+      </c>
+      <c r="C1014" t="n">
+        <v>5510</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>9163</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>1133</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>548</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>14823</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>4219</v>
+      </c>
+      <c r="I1014" t="n">
+        <v>14673</v>
+      </c>
+      <c r="J1014" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1015" t="n">
+        <v>33427</v>
+      </c>
+      <c r="C1015" t="n">
+        <v>4225</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>10890</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>934</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>529</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>13932</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>2917</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>15115</v>
+      </c>
+      <c r="J1015" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/v.6.4.1/test_data/total_latest.xlsx
+++ b/v.6.4.1/test_data/total_latest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1015"/>
+  <dimension ref="A1:J1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32425,7 +32425,7 @@
         <v>46293</v>
       </c>
       <c r="B1000" t="n">
-        <v>31778</v>
+        <v>31777</v>
       </c>
       <c r="C1000" t="n">
         <v>7700</v>
@@ -32443,7 +32443,7 @@
         <v>13544</v>
       </c>
       <c r="H1000" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="I1000" t="n">
         <v>12599</v>
@@ -32457,7 +32457,7 @@
         <v>46294</v>
       </c>
       <c r="B1001" t="n">
-        <v>33843</v>
+        <v>33842</v>
       </c>
       <c r="C1001" t="n">
         <v>6910</v>
@@ -32475,7 +32475,7 @@
         <v>11674</v>
       </c>
       <c r="H1001" t="n">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="I1001" t="n">
         <v>17865</v>
@@ -32489,7 +32489,7 @@
         <v>46295</v>
       </c>
       <c r="B1002" t="n">
-        <v>29389</v>
+        <v>29388</v>
       </c>
       <c r="C1002" t="n">
         <v>4962</v>
@@ -32507,7 +32507,7 @@
         <v>10766</v>
       </c>
       <c r="H1002" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="I1002" t="n">
         <v>14097</v>
@@ -32521,7 +32521,7 @@
         <v>46296</v>
       </c>
       <c r="B1003" t="n">
-        <v>39772</v>
+        <v>39771</v>
       </c>
       <c r="C1003" t="n">
         <v>7154</v>
@@ -32539,7 +32539,7 @@
         <v>14987</v>
       </c>
       <c r="H1003" t="n">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="I1003" t="n">
         <v>19426</v>
@@ -32553,7 +32553,7 @@
         <v>46297</v>
       </c>
       <c r="B1004" t="n">
-        <v>36064</v>
+        <v>36063</v>
       </c>
       <c r="C1004" t="n">
         <v>7778</v>
@@ -32571,7 +32571,7 @@
         <v>11329</v>
       </c>
       <c r="H1004" t="n">
-        <v>4746</v>
+        <v>4745</v>
       </c>
       <c r="I1004" t="n">
         <v>18943</v>
@@ -32585,7 +32585,7 @@
         <v>46298</v>
       </c>
       <c r="B1005" t="n">
-        <v>25223</v>
+        <v>25222</v>
       </c>
       <c r="C1005" t="n">
         <v>6502</v>
@@ -32603,7 +32603,7 @@
         <v>10423</v>
       </c>
       <c r="H1005" t="n">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="I1005" t="n">
         <v>11751</v>
@@ -32617,7 +32617,7 @@
         <v>46299</v>
       </c>
       <c r="B1006" t="n">
-        <v>30238</v>
+        <v>30237</v>
       </c>
       <c r="C1006" t="n">
         <v>5751</v>
@@ -32635,7 +32635,7 @@
         <v>11779</v>
       </c>
       <c r="H1006" t="n">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="I1006" t="n">
         <v>14730</v>
@@ -32649,7 +32649,7 @@
         <v>46300</v>
       </c>
       <c r="B1007" t="n">
-        <v>28095</v>
+        <v>28094</v>
       </c>
       <c r="C1007" t="n">
         <v>6344</v>
@@ -32667,7 +32667,7 @@
         <v>11137</v>
       </c>
       <c r="H1007" t="n">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="I1007" t="n">
         <v>14307</v>
@@ -32681,7 +32681,7 @@
         <v>46301</v>
       </c>
       <c r="B1008" t="n">
-        <v>35486</v>
+        <v>35485</v>
       </c>
       <c r="C1008" t="n">
         <v>7556</v>
@@ -32699,7 +32699,7 @@
         <v>11806</v>
       </c>
       <c r="H1008" t="n">
-        <v>4399</v>
+        <v>4398</v>
       </c>
       <c r="I1008" t="n">
         <v>17064</v>
@@ -32713,7 +32713,7 @@
         <v>46302</v>
       </c>
       <c r="B1009" t="n">
-        <v>32729</v>
+        <v>32728</v>
       </c>
       <c r="C1009" t="n">
         <v>7744</v>
@@ -32731,7 +32731,7 @@
         <v>11574</v>
       </c>
       <c r="H1009" t="n">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="I1009" t="n">
         <v>17028</v>
@@ -32745,7 +32745,7 @@
         <v>46303</v>
       </c>
       <c r="B1010" t="n">
-        <v>30867</v>
+        <v>30866</v>
       </c>
       <c r="C1010" t="n">
         <v>7007</v>
@@ -32763,7 +32763,7 @@
         <v>10909</v>
       </c>
       <c r="H1010" t="n">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="I1010" t="n">
         <v>16196</v>
@@ -32777,7 +32777,7 @@
         <v>46304</v>
       </c>
       <c r="B1011" t="n">
-        <v>27438</v>
+        <v>27436</v>
       </c>
       <c r="C1011" t="n">
         <v>6268</v>
@@ -32786,7 +32786,7 @@
         <v>7915</v>
       </c>
       <c r="E1011" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F1011" t="n">
         <v>0</v>
@@ -32795,7 +32795,7 @@
         <v>10851</v>
       </c>
       <c r="H1011" t="n">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="I1011" t="n">
         <v>14183</v>
@@ -32809,7 +32809,7 @@
         <v>46305</v>
       </c>
       <c r="B1012" t="n">
-        <v>23970</v>
+        <v>23969</v>
       </c>
       <c r="C1012" t="n">
         <v>5483</v>
@@ -32827,7 +32827,7 @@
         <v>8854</v>
       </c>
       <c r="H1012" t="n">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="I1012" t="n">
         <v>12450</v>
@@ -32841,7 +32841,7 @@
         <v>46306</v>
       </c>
       <c r="B1013" t="n">
-        <v>26891</v>
+        <v>26890</v>
       </c>
       <c r="C1013" t="n">
         <v>5106</v>
@@ -32859,7 +32859,7 @@
         <v>11495</v>
       </c>
       <c r="H1013" t="n">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="I1013" t="n">
         <v>11152</v>
@@ -32873,7 +32873,7 @@
         <v>46307</v>
       </c>
       <c r="B1014" t="n">
-        <v>35396</v>
+        <v>35395</v>
       </c>
       <c r="C1014" t="n">
         <v>5510</v>
@@ -32891,7 +32891,7 @@
         <v>14823</v>
       </c>
       <c r="H1014" t="n">
-        <v>4219</v>
+        <v>4218</v>
       </c>
       <c r="I1014" t="n">
         <v>14673</v>
@@ -32905,16 +32905,16 @@
         <v>46308</v>
       </c>
       <c r="B1015" t="n">
-        <v>33427</v>
+        <v>33424</v>
       </c>
       <c r="C1015" t="n">
         <v>4225</v>
       </c>
       <c r="D1015" t="n">
-        <v>10890</v>
+        <v>10889</v>
       </c>
       <c r="E1015" t="n">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F1015" t="n">
         <v>529</v>
@@ -32923,13 +32923,461 @@
         <v>13932</v>
       </c>
       <c r="H1015" t="n">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="I1015" t="n">
-        <v>15115</v>
+        <v>15114</v>
       </c>
       <c r="J1015" t="n">
         <v>27</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1016" t="n">
+        <v>28751</v>
+      </c>
+      <c r="C1016" t="n">
+        <v>4730</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>5588</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>853</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>469</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>13759</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>3352</v>
+      </c>
+      <c r="I1016" t="n">
+        <v>10318</v>
+      </c>
+      <c r="J1016" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1017" t="n">
+        <v>29858</v>
+      </c>
+      <c r="C1017" t="n">
+        <v>5429</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>6315</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>825</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>305</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>13769</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>3215</v>
+      </c>
+      <c r="I1017" t="n">
+        <v>11744</v>
+      </c>
+      <c r="J1017" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1018" t="n">
+        <v>31239</v>
+      </c>
+      <c r="C1018" t="n">
+        <v>5928</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>6966</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>771</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>337</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>14247</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>2990</v>
+      </c>
+      <c r="I1018" t="n">
+        <v>12894</v>
+      </c>
+      <c r="J1018" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1019" t="n">
+        <v>18780</v>
+      </c>
+      <c r="C1019" t="n">
+        <v>3504</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>3993</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>211</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>232</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>9587</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>1253</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>7497</v>
+      </c>
+      <c r="J1019" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1020" t="n">
+        <v>23199</v>
+      </c>
+      <c r="C1020" t="n">
+        <v>4266</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>3301</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>137</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>12819</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>2676</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>7567</v>
+      </c>
+      <c r="J1020" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1021" t="n">
+        <v>26755</v>
+      </c>
+      <c r="C1021" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>4444</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>976</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>228</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>12672</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>3531</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>9348</v>
+      </c>
+      <c r="J1021" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1022" t="n">
+        <v>24865</v>
+      </c>
+      <c r="C1022" t="n">
+        <v>4469</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>5422</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>937</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>283</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>11037</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>2717</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>9891</v>
+      </c>
+      <c r="J1022" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1023" t="n">
+        <v>26778</v>
+      </c>
+      <c r="C1023" t="n">
+        <v>5005</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>6230</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>798</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>316</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>10735</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>3694</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>11235</v>
+      </c>
+      <c r="J1023" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1024" t="n">
+        <v>28956</v>
+      </c>
+      <c r="C1024" t="n">
+        <v>6339</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>7152</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>883</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>338</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>10578</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>3666</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>13491</v>
+      </c>
+      <c r="J1024" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1025" t="n">
+        <v>26872</v>
+      </c>
+      <c r="C1025" t="n">
+        <v>6034</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>6682</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>885</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>409</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>10037</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>2825</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>12716</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1026" t="n">
+        <v>17507</v>
+      </c>
+      <c r="C1026" t="n">
+        <v>3780</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>4151</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>309</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>388</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>7792</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>1087</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>7931</v>
+      </c>
+      <c r="J1026" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1027" t="n">
+        <v>21282</v>
+      </c>
+      <c r="C1027" t="n">
+        <v>4146</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>3733</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>208</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>10768</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>2426</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>7879</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1028" t="n">
+        <v>31201</v>
+      </c>
+      <c r="C1028" t="n">
+        <v>5104</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>4986</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>1003</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>446</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>15909</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>3753</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>10090</v>
+      </c>
+      <c r="J1028" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1029" t="n">
+        <v>30389</v>
+      </c>
+      <c r="C1029" t="n">
+        <v>4466</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>5647</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>932</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>757</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>15501</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>3086</v>
+      </c>
+      <c r="I1029" t="n">
+        <v>10113</v>
+      </c>
+      <c r="J1029" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
